--- a/Sheets/ItemData.xlsx
+++ b/Sheets/ItemData.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60739CA-C59E-4D04-974A-FF6FA0C5B0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297F0A9F-EAFD-47C1-88A8-76A3849DEEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects" sheetId="6" r:id="rId1"/>
     <sheet name="Tools" sheetId="20" r:id="rId2"/>
     <sheet name="Crops" sheetId="19" r:id="rId3"/>
+    <sheet name="Recipe" sheetId="21" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Crops!$A$4:$G$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects!$A$4:$Q$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects!$A$4:$Q$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Recipe!$A$4:$C$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tools!$A$4:$Q$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="180">
   <si>
     <t>Parsnip Seeds</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -664,6 +666,114 @@
   </si>
   <si>
     <t>Crab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$Recipe$$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$RecipeType$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$Rep_ingredient$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COOKING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artisan Goods</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oli</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Butter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Gratin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsnip Soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>301:2,302:1,303:1,308:1,326:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>311:1,301:1,326:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>303:1,308:1,302:1,301:2,326:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>302:1,316:1,326:1,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>307:1,301:2,326:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Creamy Veggie Soup Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Gratin Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carrot Muffin Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsnip Soup Recipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COOKING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ResultItemId$</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -752,7 +862,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -792,6 +902,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -819,6 +932,14 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
@@ -996,6 +1117,149 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001480000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
+                </a:rPr>
+                <a:t>"." 값 제거 매크로</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21505" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s21505"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001540000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="32004" rIns="27432" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="맑은 고딕"/>
+                  <a:ea typeface="맑은 고딕"/>
+                </a:rPr>
+                <a:t>"." 값 제거 매크로</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21506" name="Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s21506"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002540000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1342,12 +1606,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB82EE84-0108-42B1-826D-C63A5B94B9EE}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A3:AJ45"/>
+  <dimension ref="A3:AJ58"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
@@ -1495,7 +1759,7 @@
         <v>143</v>
       </c>
       <c r="G5" s="6" t="str" cm="1">
-        <f t="array" ref="G5">_xlfn.SWITCH(F5, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G5">_xlfn.SWITCH(F5, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H5" t="s">
@@ -1541,11 +1805,11 @@
         <v>30</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" ref="C6:C45" si="0">B6&amp;"_Name"</f>
+        <f t="shared" ref="C6:C58" si="0">B6&amp;"_Name"</f>
         <v>Milk_Name</v>
       </c>
       <c r="D6" s="6" t="str">
-        <f t="shared" ref="D6:D45" si="1">B6&amp;"_Description"</f>
+        <f t="shared" ref="D6:D58" si="1">B6&amp;"_Description"</f>
         <v>Milk_Description</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -1555,7 +1819,7 @@
         <v>144</v>
       </c>
       <c r="G6" s="6" t="str" cm="1">
-        <f t="array" ref="G6">_xlfn.SWITCH(F6, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G6">_xlfn.SWITCH(F6, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H6" t="s">
@@ -1612,7 +1876,7 @@
         <v>145</v>
       </c>
       <c r="G7" s="6" t="str" cm="1">
-        <f t="array" ref="G7">_xlfn.SWITCH(F7, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G7">_xlfn.SWITCH(F7, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H7" t="s">
@@ -1666,7 +1930,7 @@
         <v>145</v>
       </c>
       <c r="G8" s="6" t="str" cm="1">
-        <f t="array" ref="G8">_xlfn.SWITCH(F8, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G8">_xlfn.SWITCH(F8, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H8" t="s">
@@ -1720,7 +1984,7 @@
         <v>145</v>
       </c>
       <c r="G9" s="6" t="str" cm="1">
-        <f t="array" ref="G9">_xlfn.SWITCH(F9, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G9">_xlfn.SWITCH(F9, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H9" t="s">
@@ -1774,7 +2038,7 @@
         <v>146</v>
       </c>
       <c r="G10" s="6" t="str" cm="1">
-        <f t="array" ref="G10">_xlfn.SWITCH(F10, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G10">_xlfn.SWITCH(F10, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DB36D3</v>
       </c>
       <c r="H10" t="s">
@@ -1828,7 +2092,7 @@
         <v>145</v>
       </c>
       <c r="G11" s="6" t="str" cm="1">
-        <f t="array" ref="G11">_xlfn.SWITCH(F11, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G11">_xlfn.SWITCH(F11, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H11" t="s">
@@ -1882,7 +2146,7 @@
         <v>145</v>
       </c>
       <c r="G12" s="6" t="str" cm="1">
-        <f t="array" ref="G12">_xlfn.SWITCH(F12, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G12">_xlfn.SWITCH(F12, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H12" t="s">
@@ -1936,7 +2200,7 @@
         <v>145</v>
       </c>
       <c r="G13" s="6" t="str" cm="1">
-        <f t="array" ref="G13">_xlfn.SWITCH(F13, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G13">_xlfn.SWITCH(F13, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H13" t="s">
@@ -1990,7 +2254,7 @@
         <v>145</v>
       </c>
       <c r="G14" s="6" t="str" cm="1">
-        <f t="array" ref="G14">_xlfn.SWITCH(F14, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G14">_xlfn.SWITCH(F14, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H14" t="s">
@@ -2044,7 +2308,7 @@
         <v>145</v>
       </c>
       <c r="G15" s="6" t="str" cm="1">
-        <f t="array" ref="G15">_xlfn.SWITCH(F15, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G15">_xlfn.SWITCH(F15, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H15" t="s">
@@ -2098,7 +2362,7 @@
         <v>145</v>
       </c>
       <c r="G16" s="6" t="str" cm="1">
-        <f t="array" ref="G16">_xlfn.SWITCH(F16, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G16">_xlfn.SWITCH(F16, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H16" t="s">
@@ -2151,7 +2415,7 @@
         <v>145</v>
       </c>
       <c r="G17" s="6" t="str" cm="1">
-        <f t="array" ref="G17">_xlfn.SWITCH(F17, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G17">_xlfn.SWITCH(F17, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H17" t="s">
@@ -2204,7 +2468,7 @@
         <v>147</v>
       </c>
       <c r="G18" s="6" t="str" cm="1">
-        <f t="array" ref="G18">_xlfn.SWITCH(F18, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G18">_xlfn.SWITCH(F18, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#0A8232</v>
       </c>
       <c r="H18" t="s">
@@ -2257,7 +2521,7 @@
         <v>147</v>
       </c>
       <c r="G19" s="6" t="str" cm="1">
-        <f t="array" ref="G19">_xlfn.SWITCH(F19, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G19">_xlfn.SWITCH(F19, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#0A8232</v>
       </c>
       <c r="H19" t="s">
@@ -2310,7 +2574,7 @@
         <v>143</v>
       </c>
       <c r="G20" s="6" t="str" cm="1">
-        <f t="array" ref="G20">_xlfn.SWITCH(F20, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G20">_xlfn.SWITCH(F20, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H20" t="s">
@@ -2363,7 +2627,7 @@
         <v>144</v>
       </c>
       <c r="G21" s="6" t="str" cm="1">
-        <f t="array" ref="G21">_xlfn.SWITCH(F21, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G21">_xlfn.SWITCH(F21, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#FF0064</v>
       </c>
       <c r="H21" t="s">
@@ -2416,7 +2680,7 @@
         <v>143</v>
       </c>
       <c r="G22" s="6" t="str" cm="1">
-        <f t="array" ref="G22">_xlfn.SWITCH(F22, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G22">_xlfn.SWITCH(F22, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H22" t="s">
@@ -2469,7 +2733,7 @@
         <v>143</v>
       </c>
       <c r="G23" s="6" t="str" cm="1">
-        <f t="array" ref="G23">_xlfn.SWITCH(F23, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G23">_xlfn.SWITCH(F23, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H23" t="s">
@@ -2522,7 +2786,7 @@
         <v>143</v>
       </c>
       <c r="G24" s="6" t="str" cm="1">
-        <f t="array" ref="G24">_xlfn.SWITCH(F24, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G24">_xlfn.SWITCH(F24, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H24" t="s">
@@ -2575,7 +2839,7 @@
         <v>143</v>
       </c>
       <c r="G25" s="6" t="str" cm="1">
-        <f t="array" ref="G25">_xlfn.SWITCH(F25, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G25">_xlfn.SWITCH(F25, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H25" t="s">
@@ -2628,7 +2892,7 @@
         <v>143</v>
       </c>
       <c r="G26" s="6" t="str" cm="1">
-        <f t="array" ref="G26">_xlfn.SWITCH(F26, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G26">_xlfn.SWITCH(F26, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H26" t="s">
@@ -2681,7 +2945,7 @@
         <v>143</v>
       </c>
       <c r="G27" s="6" t="str" cm="1">
-        <f t="array" ref="G27">_xlfn.SWITCH(F27, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G27">_xlfn.SWITCH(F27, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H27" t="s">
@@ -2734,7 +2998,7 @@
         <v>143</v>
       </c>
       <c r="G28" s="6" t="str" cm="1">
-        <f t="array" ref="G28">_xlfn.SWITCH(F28, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G28">_xlfn.SWITCH(F28, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#406672</v>
       </c>
       <c r="H28" t="s">
@@ -2767,31 +3031,31 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>401</v>
+        <v>324</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
-        <v>Starfish_Name</v>
+        <v>Salt_Name</v>
       </c>
       <c r="D29" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Starfish_Description</v>
+        <v>Salt_Description</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>42</v>
+      <c r="F29" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="G29" s="6" t="str" cm="1">
-        <f t="array" ref="G29">_xlfn.SWITCH(F29, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#00008B</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>46</v>
+        <f t="array" ref="G29">_xlfn.SWITCH(F29, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#009B6F</v>
+      </c>
+      <c r="H29" t="s">
+        <v>47</v>
       </c>
       <c r="I29" t="s">
         <v>88</v>
@@ -2800,19 +3064,19 @@
         <v>78</v>
       </c>
       <c r="K29">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
       </c>
       <c r="O29" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Q29">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <v>-300</v>
@@ -2820,31 +3084,31 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>402</v>
+        <v>325</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
-        <v>Clam_Name</v>
+        <v>Oli_Name</v>
       </c>
       <c r="D30" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Clam_Description</v>
+        <v>Oli_Description</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>42</v>
+      <c r="F30" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="G30" s="6" t="str" cm="1">
-        <f t="array" ref="G30">_xlfn.SWITCH(F30, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#00008B</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>46</v>
+        <f t="array" ref="G30">_xlfn.SWITCH(F30, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#009B6F</v>
+      </c>
+      <c r="H30" t="s">
+        <v>47</v>
       </c>
       <c r="I30" t="s">
         <v>88</v>
@@ -2853,19 +3117,19 @@
         <v>78</v>
       </c>
       <c r="K30">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
       </c>
       <c r="O30" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Q30">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R30">
         <v>-300</v>
@@ -2873,31 +3137,31 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>403</v>
+        <v>326</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
-        <v>Crab_Name</v>
+        <v>Butter_Name</v>
       </c>
       <c r="D31" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Crab_Description</v>
+        <v>Butter_Description</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>42</v>
+      <c r="F31" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="G31" s="6" t="str" cm="1">
-        <f t="array" ref="G31">_xlfn.SWITCH(F31, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#00008B</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>46</v>
+        <f t="array" ref="G31">_xlfn.SWITCH(F31, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#009B6F</v>
+      </c>
+      <c r="H31" t="s">
+        <v>47</v>
       </c>
       <c r="I31" t="s">
         <v>88</v>
@@ -2906,7 +3170,7 @@
         <v>78</v>
       </c>
       <c r="K31">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -2918,39 +3182,39 @@
         <v>1</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>10</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>404</v>
+        <v>327</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
-        <v>Fish_Name</v>
+        <v>Creamy Veggie Soup_Name</v>
       </c>
       <c r="D32" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Fish_Description</v>
+        <v>Creamy Veggie Soup_Description</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>42</v>
+      <c r="F32" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="G32" s="6" t="str" cm="1">
-        <f t="array" ref="G32">_xlfn.SWITCH(F32, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#00008B</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>46</v>
+        <f t="array" ref="G32">_xlfn.SWITCH(F32, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H32" t="s">
+        <v>177</v>
       </c>
       <c r="I32" t="s">
         <v>88</v>
@@ -2959,7 +3223,7 @@
         <v>78</v>
       </c>
       <c r="K32">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -2971,39 +3235,39 @@
         <v>1</v>
       </c>
       <c r="Q32">
+        <v>120</v>
+      </c>
+      <c r="R32">
         <v>50</v>
-      </c>
-      <c r="R32">
-        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>501</v>
+        <v>328</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
-        <v>Acorn_Name</v>
+        <v>Bread_Name</v>
       </c>
       <c r="D33" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Acorn_Description</v>
+        <v>Bread_Description</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>147</v>
+      <c r="F33" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="G33" s="6" t="str" cm="1">
-        <f t="array" ref="G33">_xlfn.SWITCH(F33, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#0A8232</v>
+        <f t="array" ref="G33">_xlfn.SWITCH(F33, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
       <c r="I33" t="s">
         <v>88</v>
@@ -3012,7 +3276,7 @@
         <v>78</v>
       </c>
       <c r="K33">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -3024,39 +3288,39 @@
         <v>1</v>
       </c>
       <c r="Q33">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="R33">
-        <v>-300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>502</v>
+        <v>329</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
-        <v>Crate_Name</v>
+        <v>Potato Gratin_Name</v>
       </c>
       <c r="D34" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Crate_Description</v>
+        <v>Potato Gratin_Description</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>148</v>
+      <c r="F34" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="G34" s="6" t="str" cm="1">
-        <f t="array" ref="G34">_xlfn.SWITCH(F34, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#943D28</v>
+        <f t="array" ref="G34">_xlfn.SWITCH(F34, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
       <c r="I34" t="s">
         <v>88</v>
@@ -3065,51 +3329,51 @@
         <v>78</v>
       </c>
       <c r="K34">
+        <v>103</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34">
         <v>120</v>
       </c>
-      <c r="N34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P34" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>1000</v>
-      </c>
       <c r="R34">
-        <v>-300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>601</v>
+        <v>330</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
-        <v>Carrot Seeds_Name</v>
+        <v>Carrot Muffin_Name</v>
       </c>
       <c r="D35" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Carrot Seeds_Description</v>
+        <v>Carrot Muffin_Description</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>149</v>
+      <c r="F35" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="G35" s="6" t="str" cm="1">
-        <f t="array" ref="G35">_xlfn.SWITCH(F35, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>45</v>
+        <f t="array" ref="G35">_xlfn.SWITCH(F35, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H35" t="s">
+        <v>177</v>
       </c>
       <c r="I35" t="s">
         <v>88</v>
@@ -3118,7 +3382,7 @@
         <v>78</v>
       </c>
       <c r="K35">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -3130,39 +3394,39 @@
         <v>1</v>
       </c>
       <c r="Q35">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="R35">
-        <v>-300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>602</v>
+        <v>331</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
-        <v>Cauliflower Seeds_Name</v>
+        <v>Parsnip Soup_Name</v>
       </c>
       <c r="D36" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Cauliflower Seeds_Description</v>
+        <v>Parsnip Soup_Description</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>149</v>
+      <c r="F36" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="G36" s="6" t="str" cm="1">
-        <f t="array" ref="G36">_xlfn.SWITCH(F36, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>45</v>
+        <f t="array" ref="G36">_xlfn.SWITCH(F36, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H36" t="s">
+        <v>177</v>
       </c>
       <c r="I36" t="s">
         <v>88</v>
@@ -3171,7 +3435,7 @@
         <v>78</v>
       </c>
       <c r="K36">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -3183,39 +3447,39 @@
         <v>1</v>
       </c>
       <c r="Q36">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="R36">
-        <v>-300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>603</v>
+        <v>401</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
-        <v>Pumpkin Seeds_Name</v>
+        <v>Starfish_Name</v>
       </c>
       <c r="D37" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Pumpkin Seeds_Description</v>
+        <v>Starfish_Description</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="G37" s="6" t="str" cm="1">
-        <f t="array" ref="G37">_xlfn.SWITCH(F37, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
+        <f t="array" ref="G37">_xlfn.SWITCH(F37, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#00008B</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I37" t="s">
         <v>88</v>
@@ -3224,7 +3488,7 @@
         <v>78</v>
       </c>
       <c r="K37">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -3236,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="Q37">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="R37">
         <v>-300</v>
@@ -3244,31 +3508,31 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>604</v>
+        <v>402</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
-        <v>Sunflower Seeds_Name</v>
+        <v>Clam_Name</v>
       </c>
       <c r="D38" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Sunflower Seeds_Description</v>
+        <v>Clam_Description</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="G38" s="6" t="str" cm="1">
-        <f t="array" ref="G38">_xlfn.SWITCH(F38, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
+        <f t="array" ref="G38">_xlfn.SWITCH(F38, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#00008B</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I38" t="s">
         <v>88</v>
@@ -3277,7 +3541,7 @@
         <v>78</v>
       </c>
       <c r="K38">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -3289,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="Q38">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="R38">
         <v>-300</v>
@@ -3297,31 +3561,31 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>605</v>
+        <v>403</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
-        <v>Radish Seeds_Name</v>
+        <v>Crab_Name</v>
       </c>
       <c r="D39" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Radish Seeds_Description</v>
+        <v>Crab_Description</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="G39" s="6" t="str" cm="1">
-        <f t="array" ref="G39">_xlfn.SWITCH(F39, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
+        <f t="array" ref="G39">_xlfn.SWITCH(F39, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#00008B</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I39" t="s">
         <v>88</v>
@@ -3330,7 +3594,7 @@
         <v>78</v>
       </c>
       <c r="K39">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -3342,39 +3606,39 @@
         <v>1</v>
       </c>
       <c r="Q39">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>-300</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>606</v>
+        <v>404</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
-        <v>Parsnip Seeds_Name</v>
+        <v>Fish_Name</v>
       </c>
       <c r="D40" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Parsnip Seeds_Description</v>
+        <v>Fish_Description</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="G40" s="6" t="str" cm="1">
-        <f t="array" ref="G40">_xlfn.SWITCH(F40, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
+        <f t="array" ref="G40">_xlfn.SWITCH(F40, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#00008B</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I40" t="s">
         <v>88</v>
@@ -3383,7 +3647,7 @@
         <v>78</v>
       </c>
       <c r="K40">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -3395,39 +3659,39 @@
         <v>1</v>
       </c>
       <c r="Q40">
+        <v>50</v>
+      </c>
+      <c r="R40">
         <v>10</v>
-      </c>
-      <c r="R40">
-        <v>-300</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
-        <v>Potato Seeds_Name</v>
+        <v>Acorn_Name</v>
       </c>
       <c r="D41" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Potato Seeds_Description</v>
+        <v>Acorn_Description</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G41" s="6" t="str" cm="1">
-        <f t="array" ref="G41">_xlfn.SWITCH(F41, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>45</v>
+        <f t="array" ref="G41">_xlfn.SWITCH(F41, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#0A8232</v>
+      </c>
+      <c r="H41" t="s">
+        <v>44</v>
       </c>
       <c r="I41" t="s">
         <v>88</v>
@@ -3436,7 +3700,7 @@
         <v>78</v>
       </c>
       <c r="K41">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -3448,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="Q41">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R41">
         <v>-300</v>
@@ -3456,31 +3720,31 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>608</v>
+        <v>502</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
-        <v>Red Cabbage Seeds_Name</v>
+        <v>Crate_Name</v>
       </c>
       <c r="D42" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Red Cabbage Seeds_Description</v>
+        <v>Crate_Description</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G42" s="6" t="str" cm="1">
-        <f t="array" ref="G42">_xlfn.SWITCH(F42, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
-        <v>#A52A2A</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>45</v>
+        <f t="array" ref="G42">_xlfn.SWITCH(F42, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#943D28</v>
+      </c>
+      <c r="H42" t="s">
+        <v>44</v>
       </c>
       <c r="I42" t="s">
         <v>88</v>
@@ -3489,19 +3753,19 @@
         <v>78</v>
       </c>
       <c r="K42">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
       </c>
       <c r="O42" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="R42">
         <v>-300</v>
@@ -3509,18 +3773,18 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
-        <v>Beetroot Seeds_Name</v>
+        <v>Carrot Seeds_Name</v>
       </c>
       <c r="D43" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Beetroot Seeds_Description</v>
+        <v>Carrot Seeds_Description</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>85</v>
@@ -3529,7 +3793,7 @@
         <v>149</v>
       </c>
       <c r="G43" s="6" t="str" cm="1">
-        <f t="array" ref="G43">_xlfn.SWITCH(F43, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G43">_xlfn.SWITCH(F43, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#A52A2A</v>
       </c>
       <c r="H43" s="9" t="s">
@@ -3539,10 +3803,10 @@
         <v>88</v>
       </c>
       <c r="J43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K43">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -3554,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="Q43">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R43">
         <v>-300</v>
@@ -3562,18 +3826,18 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
-        <v>Wheat Seeds_Name</v>
+        <v>Cauliflower Seeds_Name</v>
       </c>
       <c r="D44" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Wheat Seeds_Description</v>
+        <v>Cauliflower Seeds_Description</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>
@@ -3582,7 +3846,7 @@
         <v>149</v>
       </c>
       <c r="G44" s="6" t="str" cm="1">
-        <f t="array" ref="G44">_xlfn.SWITCH(F44, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G44">_xlfn.SWITCH(F44, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#A52A2A</v>
       </c>
       <c r="H44" s="9" t="s">
@@ -3592,10 +3856,10 @@
         <v>88</v>
       </c>
       <c r="J44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K44">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -3607,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="Q44">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="R44">
         <v>-300</v>
@@ -3615,18 +3879,18 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
-        <v>Kale Seeds_Name</v>
+        <v>Pumpkin Seeds_Name</v>
       </c>
       <c r="D45" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Kale Seeds_Description</v>
+        <v>Pumpkin Seeds_Description</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>85</v>
@@ -3635,7 +3899,7 @@
         <v>149</v>
       </c>
       <c r="G45" s="6" t="str" cm="1">
-        <f t="array" ref="G45">_xlfn.SWITCH(F45, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G45">_xlfn.SWITCH(F45, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#A52A2A</v>
       </c>
       <c r="H45" s="9" t="s">
@@ -3645,10 +3909,10 @@
         <v>88</v>
       </c>
       <c r="J45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K45">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -3660,15 +3924,629 @@
         <v>1</v>
       </c>
       <c r="Q45">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="R45">
         <v>-300</v>
       </c>
     </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>604</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunflower Seeds_Name</v>
+      </c>
+      <c r="D46" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Sunflower Seeds_Description</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G46" s="6" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.SWITCH(F46, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I46" t="s">
+        <v>88</v>
+      </c>
+      <c r="J46" t="s">
+        <v>77</v>
+      </c>
+      <c r="K46">
+        <v>24</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P46" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <v>20</v>
+      </c>
+      <c r="R46">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>605</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>Radish Seeds_Name</v>
+      </c>
+      <c r="D47" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Radish Seeds_Description</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="6" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.SWITCH(F47, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" t="s">
+        <v>88</v>
+      </c>
+      <c r="J47" t="s">
+        <v>77</v>
+      </c>
+      <c r="K47">
+        <v>32</v>
+      </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q47">
+        <v>20</v>
+      </c>
+      <c r="R47">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>606</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v>Parsnip Seeds_Name</v>
+      </c>
+      <c r="D48" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Parsnip Seeds_Description</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48" s="6" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.SWITCH(F48, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I48" t="s">
+        <v>88</v>
+      </c>
+      <c r="J48" t="s">
+        <v>77</v>
+      </c>
+      <c r="K48">
+        <v>40</v>
+      </c>
+      <c r="N48" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q48">
+        <v>10</v>
+      </c>
+      <c r="R48">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>607</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v>Potato Seeds_Name</v>
+      </c>
+      <c r="D49" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Potato Seeds_Description</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G49" s="6" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.SWITCH(F49, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I49" t="s">
+        <v>88</v>
+      </c>
+      <c r="J49" t="s">
+        <v>77</v>
+      </c>
+      <c r="K49">
+        <v>48</v>
+      </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P49" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q49">
+        <v>25</v>
+      </c>
+      <c r="R49">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>608</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v>Red Cabbage Seeds_Name</v>
+      </c>
+      <c r="D50" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Red Cabbage Seeds_Description</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G50" s="6" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.SWITCH(F50, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I50" t="s">
+        <v>88</v>
+      </c>
+      <c r="J50" t="s">
+        <v>77</v>
+      </c>
+      <c r="K50">
+        <v>56</v>
+      </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P50" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q50">
+        <v>50</v>
+      </c>
+      <c r="R50">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>609</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v>Beetroot Seeds_Name</v>
+      </c>
+      <c r="D51" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Beetroot Seeds_Description</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G51" s="6" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.SWITCH(F51, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I51" t="s">
+        <v>88</v>
+      </c>
+      <c r="J51" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51">
+        <v>64</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P51" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q51">
+        <v>10</v>
+      </c>
+      <c r="R51">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>610</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="0"/>
+        <v>Wheat Seeds_Name</v>
+      </c>
+      <c r="D52" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Wheat Seeds_Description</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G52" s="6" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.SWITCH(F52, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I52" t="s">
+        <v>88</v>
+      </c>
+      <c r="J52" t="s">
+        <v>77</v>
+      </c>
+      <c r="K52">
+        <v>72</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P52" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q52">
+        <v>5</v>
+      </c>
+      <c r="R52">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>611</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="0"/>
+        <v>Kale Seeds_Name</v>
+      </c>
+      <c r="D53" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Kale Seeds_Description</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G53" s="6" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.SWITCH(F53, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#A52A2A</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J53" t="s">
+        <v>77</v>
+      </c>
+      <c r="K53">
+        <v>80</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P53" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q53">
+        <v>35</v>
+      </c>
+      <c r="R53">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>801</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="0"/>
+        <v>Creamy Veggie Soup Recipe_Name</v>
+      </c>
+      <c r="D54" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Creamy Veggie Soup Recipe_Description</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G54" s="6" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.SWITCH(F54, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I54" t="s">
+        <v>88</v>
+      </c>
+      <c r="J54" t="s">
+        <v>78</v>
+      </c>
+      <c r="K54">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>802</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="0"/>
+        <v>Bread Recipe_Name</v>
+      </c>
+      <c r="D55" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Bread Recipe_Description</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G55" s="6" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.SWITCH(F55, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" t="s">
+        <v>88</v>
+      </c>
+      <c r="J55" t="s">
+        <v>78</v>
+      </c>
+      <c r="K55">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>803</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="0"/>
+        <v>Potato Gratin Recipe_Name</v>
+      </c>
+      <c r="D56" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Potato Gratin Recipe_Description</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G56" s="6" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.SWITCH(F56, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I56" t="s">
+        <v>88</v>
+      </c>
+      <c r="J56" t="s">
+        <v>78</v>
+      </c>
+      <c r="K56">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>804</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="0"/>
+        <v>Carrot Muffin Recipe_Name</v>
+      </c>
+      <c r="D57" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Carrot Muffin Recipe_Description</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G57" s="6" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.SWITCH(F57, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I57" t="s">
+        <v>88</v>
+      </c>
+      <c r="J57" t="s">
+        <v>78</v>
+      </c>
+      <c r="K57">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>805</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="0"/>
+        <v>Parsnip Soup Recipe_Name</v>
+      </c>
+      <c r="D58" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>Parsnip Soup Recipe_Description</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G58" s="6" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.SWITCH(F58, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
+        <v>#DC3C00</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I58" t="s">
+        <v>88</v>
+      </c>
+      <c r="J58" t="s">
+        <v>78</v>
+      </c>
+      <c r="K58">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:S35">
-    <sortCondition ref="A5:A35"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:S43">
+    <sortCondition ref="A5:A43"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3861,7 +4739,7 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="str" cm="1">
-        <f t="array" ref="G5">_xlfn.SWITCH(F5, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G5">_xlfn.SWITCH(F5, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H5" t="s">
@@ -3907,7 +4785,7 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="str" cm="1">
-        <f t="array" ref="G6">_xlfn.SWITCH(F6, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G6">_xlfn.SWITCH(F6, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H6" t="s">
@@ -3956,7 +4834,7 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="str" cm="1">
-        <f t="array" ref="G7">_xlfn.SWITCH(F7, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G7">_xlfn.SWITCH(F7, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H7" t="s">
@@ -4005,7 +4883,7 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="str" cm="1">
-        <f t="array" ref="G8">_xlfn.SWITCH(F8, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G8">_xlfn.SWITCH(F8, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H8" t="s">
@@ -4054,7 +4932,7 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="str" cm="1">
-        <f t="array" ref="G9">_xlfn.SWITCH(F9, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G9">_xlfn.SWITCH(F9, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H9" t="s">
@@ -4100,7 +4978,7 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="str" cm="1">
-        <f t="array" ref="G10">_xlfn.SWITCH(F10, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G10">_xlfn.SWITCH(F10, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H10" t="s">
@@ -4149,7 +5027,7 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="str" cm="1">
-        <f t="array" ref="G11">_xlfn.SWITCH(F11, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G11">_xlfn.SWITCH(F11, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H11" t="s">
@@ -4198,7 +5076,7 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="str" cm="1">
-        <f t="array" ref="G12">_xlfn.SWITCH(F12, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G12">_xlfn.SWITCH(F12, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H12" t="s">
@@ -4247,7 +5125,7 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="str" cm="1">
-        <f t="array" ref="G13">_xlfn.SWITCH(F13, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G13">_xlfn.SWITCH(F13, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H13" t="s">
@@ -4293,7 +5171,7 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="str" cm="1">
-        <f t="array" ref="G14">_xlfn.SWITCH(F14, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G14">_xlfn.SWITCH(F14, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H14" t="s">
@@ -4342,7 +5220,7 @@
         <v>151</v>
       </c>
       <c r="G15" s="6" t="str" cm="1">
-        <f t="array" ref="G15">_xlfn.SWITCH(F15, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G15">_xlfn.SWITCH(F15, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H15" t="s">
@@ -4391,7 +5269,7 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="str" cm="1">
-        <f t="array" ref="G16">_xlfn.SWITCH(F16, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G16">_xlfn.SWITCH(F16, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H16" t="s">
@@ -4440,7 +5318,7 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="str" cm="1">
-        <f t="array" ref="G17">_xlfn.SWITCH(F17, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G17">_xlfn.SWITCH(F17, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H17" t="s">
@@ -4486,7 +5364,7 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="str" cm="1">
-        <f t="array" ref="G18">_xlfn.SWITCH(F18, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G18">_xlfn.SWITCH(F18, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H18" t="s">
@@ -4535,7 +5413,7 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="str" cm="1">
-        <f t="array" ref="G19">_xlfn.SWITCH(F19, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G19">_xlfn.SWITCH(F19, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H19" t="s">
@@ -4584,7 +5462,7 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="str" cm="1">
-        <f t="array" ref="G20">_xlfn.SWITCH(F20, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G20">_xlfn.SWITCH(F20, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H20" t="s">
@@ -4633,7 +5511,7 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="str" cm="1">
-        <f t="array" ref="G21">_xlfn.SWITCH(F21, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G21">_xlfn.SWITCH(F21, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H21" t="s">
@@ -4679,7 +5557,7 @@
         <v>151</v>
       </c>
       <c r="G22" s="6" t="str" cm="1">
-        <f t="array" ref="G22">_xlfn.SWITCH(F22, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G22">_xlfn.SWITCH(F22, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H22" t="s">
@@ -4728,7 +5606,7 @@
         <v>151</v>
       </c>
       <c r="G23" s="6" t="str" cm="1">
-        <f t="array" ref="G23">_xlfn.SWITCH(F23, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G23">_xlfn.SWITCH(F23, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H23" t="s">
@@ -4777,7 +5655,7 @@
         <v>151</v>
       </c>
       <c r="G24" s="6" t="str" cm="1">
-        <f t="array" ref="G24">_xlfn.SWITCH(F24, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131", "미지정")</f>
+        <f t="array" ref="G24">_xlfn.SWITCH(F24, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "미지정")</f>
         <v>#313131</v>
       </c>
       <c r="H24" t="s">
@@ -5676,4 +6554,384 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E48E9B5-8DF3-4A27-BCBE-50E6A0712D00}">
+  <dimension ref="A3:W53"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="19" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+    </row>
+    <row r="4" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>801</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5">
+        <v>327</v>
+      </c>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>802</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6">
+        <v>328</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>803</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7">
+        <v>329</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>804</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8">
+        <v>330</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>805</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9">
+        <v>331</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B10" s="5"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B11" s="5"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B12" s="5"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B13" s="5"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B14" s="5"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B15" s="5"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B16" s="5"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="5"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="5"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="5"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="5"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="5"/>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="5"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="5"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="5"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="5"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B37" s="5"/>
+      <c r="C37" s="9"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="5"/>
+      <c r="C38" s="9"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="5"/>
+      <c r="C39" s="9"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B40" s="5"/>
+      <c r="C40" s="9"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="5"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B43" s="5"/>
+      <c r="C43" s="9"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B44" s="5"/>
+      <c r="C44" s="9"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B45" s="5"/>
+      <c r="C45" s="9"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B46" s="5"/>
+      <c r="C46" s="9"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B47" s="5"/>
+      <c r="C47" s="9"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="5"/>
+      <c r="C48" s="9"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="5"/>
+      <c r="C49" s="9"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" s="5"/>
+      <c r="C50" s="9"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="5"/>
+      <c r="C51" s="9"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B52" s="5"/>
+      <c r="C52" s="9"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B53" s="5"/>
+      <c r="C53" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="21506" r:id="rId4" name="Button 2">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>0</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="21505" r:id="rId5" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!DeleteSpecificValueCells">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>0</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
 </file>
--- a/Sheets/ItemData.xlsx
+++ b/Sheets/ItemData.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297F0A9F-EAFD-47C1-88A8-76A3849DEEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0526128E-2A3F-470D-B933-6F44BF1A774B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-285" yWindow="30" windowWidth="28770" windowHeight="15450" activeTab="3" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects" sheetId="6" r:id="rId1"/>
     <sheet name="Tools" sheetId="20" r:id="rId2"/>
     <sheet name="Crops" sheetId="19" r:id="rId3"/>
-    <sheet name="Recipe" sheetId="21" r:id="rId4"/>
+    <sheet name="Recipes" sheetId="21" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Crops!$A$4:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Objects!$A$4:$Q$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Recipe!$A$4:$C$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Recipes!$A$4:$C$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tools!$A$4:$Q$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -669,10 +669,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>$$Recipe$$</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>$RecipeType$</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -774,6 +770,10 @@
   </si>
   <si>
     <t>$ResultItemId$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$Recipes$$</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3034,7 +3034,7 @@
         <v>324</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -3048,7 +3048,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G29" s="6" t="str" cm="1">
         <f t="array" ref="G29">_xlfn.SWITCH(F29, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
@@ -3087,7 +3087,7 @@
         <v>325</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -3101,7 +3101,7 @@
         <v>85</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G30" s="6" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.SWITCH(F30, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
@@ -3140,7 +3140,7 @@
         <v>326</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -3154,7 +3154,7 @@
         <v>85</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G31" s="6" t="str" cm="1">
         <f t="array" ref="G31">_xlfn.SWITCH(F31, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
@@ -3193,7 +3193,7 @@
         <v>327</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -3207,14 +3207,14 @@
         <v>85</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G32" s="6" t="str" cm="1">
         <f t="array" ref="G32">_xlfn.SWITCH(F32, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I32" t="s">
         <v>88</v>
@@ -3246,7 +3246,7 @@
         <v>328</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -3260,14 +3260,14 @@
         <v>85</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G33" s="6" t="str" cm="1">
         <f t="array" ref="G33">_xlfn.SWITCH(F33, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I33" t="s">
         <v>88</v>
@@ -3299,7 +3299,7 @@
         <v>329</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -3313,14 +3313,14 @@
         <v>85</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G34" s="6" t="str" cm="1">
         <f t="array" ref="G34">_xlfn.SWITCH(F34, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I34" t="s">
         <v>88</v>
@@ -3352,7 +3352,7 @@
         <v>330</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -3366,14 +3366,14 @@
         <v>85</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G35" s="6" t="str" cm="1">
         <f t="array" ref="G35">_xlfn.SWITCH(F35, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I35" t="s">
         <v>88</v>
@@ -3405,7 +3405,7 @@
         <v>331</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -3419,14 +3419,14 @@
         <v>85</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G36" s="6" t="str" cm="1">
         <f t="array" ref="G36">_xlfn.SWITCH(F36, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I36" t="s">
         <v>88</v>
@@ -4359,7 +4359,7 @@
         <v>801</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -4373,14 +4373,14 @@
         <v>85</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G54" s="6" t="str" cm="1">
         <f t="array" ref="G54">_xlfn.SWITCH(F54, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I54" t="s">
         <v>88</v>
@@ -4397,7 +4397,7 @@
         <v>802</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -4411,14 +4411,14 @@
         <v>85</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G55" s="6" t="str" cm="1">
         <f t="array" ref="G55">_xlfn.SWITCH(F55, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I55" t="s">
         <v>88</v>
@@ -4435,7 +4435,7 @@
         <v>803</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -4449,14 +4449,14 @@
         <v>85</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G56" s="6" t="str" cm="1">
         <f t="array" ref="G56">_xlfn.SWITCH(F56, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I56" t="s">
         <v>88</v>
@@ -4473,7 +4473,7 @@
         <v>804</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -4487,14 +4487,14 @@
         <v>85</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G57" s="6" t="str" cm="1">
         <f t="array" ref="G57">_xlfn.SWITCH(F57, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I57" t="s">
         <v>88</v>
@@ -4511,7 +4511,7 @@
         <v>805</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -4525,14 +4525,14 @@
         <v>85</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G58" s="6" t="str" cm="1">
         <f t="array" ref="G58">_xlfn.SWITCH(F58, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I58" t="s">
         <v>88</v>
@@ -6575,7 +6575,7 @@
   <sheetData>
     <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
@@ -6607,13 +6607,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="E4" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -6627,13 +6627,13 @@
         <v>801</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E5">
         <v>327</v>
@@ -6645,13 +6645,13 @@
         <v>802</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E6">
         <v>328</v>
@@ -6663,13 +6663,13 @@
         <v>803</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E7">
         <v>329</v>
@@ -6681,13 +6681,13 @@
         <v>804</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E8">
         <v>330</v>
@@ -6700,13 +6700,13 @@
         <v>805</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E9">
         <v>331</v>

--- a/Sheets/ItemData.xlsx
+++ b/Sheets/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0526128E-2A3F-470D-B933-6F44BF1A774B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B7DA06-3B99-459D-8143-F3F142803D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-285" yWindow="30" windowWidth="28770" windowHeight="15450" activeTab="3" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Objects" sheetId="6" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="182">
   <si>
     <t>Parsnip Seeds</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -673,10 +673,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>$Rep_ingredient$</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Recipe</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -774,6 +770,18 @@
   </si>
   <si>
     <t>$$Recipes$$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECTS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RECIPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$Req_ingredient$</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3034,7 +3042,7 @@
         <v>324</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -3048,7 +3056,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G29" s="6" t="str" cm="1">
         <f t="array" ref="G29">_xlfn.SWITCH(F29, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
@@ -3087,7 +3095,7 @@
         <v>325</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -3101,7 +3109,7 @@
         <v>85</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G30" s="6" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.SWITCH(F30, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
@@ -3140,7 +3148,7 @@
         <v>326</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -3154,7 +3162,7 @@
         <v>85</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G31" s="6" t="str" cm="1">
         <f t="array" ref="G31">_xlfn.SWITCH(F31, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
@@ -3193,7 +3201,7 @@
         <v>327</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -3207,14 +3215,14 @@
         <v>85</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G32" s="6" t="str" cm="1">
         <f t="array" ref="G32">_xlfn.SWITCH(F32, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I32" t="s">
         <v>88</v>
@@ -3246,7 +3254,7 @@
         <v>328</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -3260,14 +3268,14 @@
         <v>85</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G33" s="6" t="str" cm="1">
         <f t="array" ref="G33">_xlfn.SWITCH(F33, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I33" t="s">
         <v>88</v>
@@ -3299,7 +3307,7 @@
         <v>329</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -3313,14 +3321,14 @@
         <v>85</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G34" s="6" t="str" cm="1">
         <f t="array" ref="G34">_xlfn.SWITCH(F34, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I34" t="s">
         <v>88</v>
@@ -3352,7 +3360,7 @@
         <v>330</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -3366,14 +3374,14 @@
         <v>85</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G35" s="6" t="str" cm="1">
         <f t="array" ref="G35">_xlfn.SWITCH(F35, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I35" t="s">
         <v>88</v>
@@ -3405,7 +3413,7 @@
         <v>331</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -3419,14 +3427,14 @@
         <v>85</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G36" s="6" t="str" cm="1">
         <f t="array" ref="G36">_xlfn.SWITCH(F36, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I36" t="s">
         <v>88</v>
@@ -4359,7 +4367,7 @@
         <v>801</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -4370,17 +4378,17 @@
         <v>Creamy Veggie Soup Recipe_Description</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G54" s="6" t="str" cm="1">
         <f t="array" ref="G54">_xlfn.SWITCH(F54, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I54" t="s">
         <v>88</v>
@@ -4397,7 +4405,7 @@
         <v>802</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -4411,14 +4419,14 @@
         <v>85</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G55" s="6" t="str" cm="1">
         <f t="array" ref="G55">_xlfn.SWITCH(F55, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I55" t="s">
         <v>88</v>
@@ -4435,7 +4443,7 @@
         <v>803</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -4449,14 +4457,14 @@
         <v>85</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G56" s="6" t="str" cm="1">
         <f t="array" ref="G56">_xlfn.SWITCH(F56, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I56" t="s">
         <v>88</v>
@@ -4473,7 +4481,7 @@
         <v>804</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -4487,14 +4495,14 @@
         <v>85</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G57" s="6" t="str" cm="1">
         <f t="array" ref="G57">_xlfn.SWITCH(F57, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I57" t="s">
         <v>88</v>
@@ -4511,7 +4519,7 @@
         <v>805</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -4525,14 +4533,14 @@
         <v>85</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G58" s="6" t="str" cm="1">
         <f t="array" ref="G58">_xlfn.SWITCH(F58, "Resource", "#406672", "Animal Product", "#FF0064", "Vegetable", "#FF0064", "Fruit","#FF1493","Flower", "#DB36D3","Forage", "#0A8232","Recipe", "#DC3C00","Fish", "#00008B","Seed", "#A52A2A","Crafting", "#943D28","Mineral", "#6E005A", "Trash", "#696969","BASIC", "#313131","Tool", "#313131","Artisan Goods", "#009B6F", "Cooking", "#DC3C00","미지정")</f>
         <v>#DC3C00</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I58" t="s">
         <v>88</v>
@@ -6575,7 +6583,7 @@
   <sheetData>
     <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
@@ -6610,10 +6618,10 @@
         <v>153</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -6627,13 +6635,13 @@
         <v>801</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E5">
         <v>327</v>
@@ -6645,13 +6653,13 @@
         <v>802</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E6">
         <v>328</v>
@@ -6663,13 +6671,13 @@
         <v>803</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E7">
         <v>329</v>
@@ -6681,13 +6689,13 @@
         <v>804</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E8">
         <v>330</v>
@@ -6700,13 +6708,13 @@
         <v>805</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E9">
         <v>331</v>
